--- a/docs/planning/QA엑셀-v1/김유석/QA 담양 중대재해 시스템 관리 김유석.xlsx
+++ b/docs/planning/QA엑셀-v1/김유석/QA 담양 중대재해 시스템 관리 김유석.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'사용자·권한'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'기준정보'!$A$3:$I$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'기준정보'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'연계·알림'!$A$3:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'연계·알림'!$A$3:$I$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'연계·알림'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,9 +55,9 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="000563C1"/>
       <sz val="10.5"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -110,6 +110,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00A6A6A6"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -286,7 +292,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -784,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -843,12 +849,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>이 파일</t>
+          <t>내 계정</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>시스템 관리는 박안전에게만 보입니다. 권한 설정을 바꿔도 실제 메뉴 노출은 바뀌지 않는 것이 정상입니다.</t>
+          <t>QA박안전5 (재난안전과 담당자) · QA하정수5 (내 부서 보건소 담당 공무원)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -858,15 +864,15 @@
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>줄 수</t>
+          <t>이 파일</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10줄</t>
+          <t>시스템 관리 권한을 받은 QA박안전5 계정으로 합니다 — 그 창 맨 위에 «시스템 관리»가 없으면 QA박안전5 줄은 모두 «확인 불가». 여기 설정은 다른 사람 화면에 바로 영향을 주므로 내가 만든 «김유석_…» 항목만 바꾸고, 기존 값을 바꿨으면 같은 줄에서 되돌립니다.</t>
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -879,12 +885,12 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>줄 수</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>사용자·권한 → 기준정보 → 연계·알림</t>
+          <t>11줄</t>
         </is>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -897,12 +903,12 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>테스트 주소</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>(배포 주소를 받으면 채웁니다)</t>
+          <t>시트</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>사용자·권한 → 기준정보 → 연계·알림</t>
         </is>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -915,10 +921,14 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>브라우저</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
+          <t>테스트 주소</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>https://safety.damyang.go.kr/login</t>
+        </is>
+      </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
@@ -929,7 +939,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>기기</t>
+          <t>브라우저</t>
         </is>
       </c>
       <c r="B10" s="7" t="n"/>
@@ -943,10 +953,10 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>시작한 날</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
+          <t>기기</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
@@ -954,82 +964,78 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시작한 날</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>이렇게 하면 됩니다</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>① 브라우저로 위 «테스트 주소»를 엽니다. 시트마다 맨 위에 «새 탭에서 시작» 또는 «같은 탭에서 이어서»가 적혀 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>② 화면 오른쪽 위 이름을 눌러 «누구로» 칸의 사람으로 바꿉니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+          <t>① 위 «테스트 주소»에서 받은 아이디·비밀번호로 로그인합니다. 로그인하면 통합 현황 화면으로 갑니다. 5번 틀리면 계정이 잠깁니다 — 담당 개발자에게 풀어 달라고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>③ «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
+          <t>② 내 계정 두 개를 창 두 개에 따로 로그인해 둡니다 — 일반 창에는 QA박안전5(재난안전과), 시크릿 창(Ctrl + Shift + N · 맥 Cmd + Shift + N)에는 QA하정수5(담당 공무원). 두 창을 나란히 두면 계정을 바꿀 필요가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+          <t>③ «누구로» 칸에 적힌 계정의 창에서 «어디서» 메뉴로 가서 «해 볼 것»대로 눌러 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>④ «이러면 성공»과 같으면 «결과» 칸에서 성공을, 다르면 실패·오류 등을 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>⑤ 실패·오류·문의면 «메모»에 한 줄 적고, 필요하면 «사진» 칸에 화면 캡처를 붙여넣습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>결과 고르는 법</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>이럴 때 고르세요</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C22" s="4" t="n"/>
@@ -1040,14 +1046,14 @@
       <c r="H22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>실패</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>성공</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
+          <t>«이러면 성공»대로 된다</t>
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
@@ -1058,14 +1064,14 @@
       <c r="H23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>오류</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>실패</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
+          <t>되긴 하는데 설명과 다르다 — 막혀야 하는데 저장된다, 문구·숫자가 틀리다</t>
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
@@ -1076,14 +1082,14 @@
       <c r="H24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>보류</t>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>오류</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
+          <t>화면이 멈추거나 깨진다, 눌러도 아무 일이 없다, 오류 창이 뜬다</t>
         </is>
       </c>
       <c r="C25" s="4" t="n"/>
@@ -1094,14 +1100,14 @@
       <c r="H25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>보류</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
+          <t>앞 단계가 안 돼서 지금은 못 한다 — 메모에 이유</t>
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
@@ -1112,14 +1118,14 @@
       <c r="H26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>문의</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+          <t>이 환경에서는 볼 수 없다 — 예: 확인할 데이터가 없다</t>
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
@@ -1129,256 +1135,216 @@
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>맞는지 헷갈린다 — 메모에 궁금한 점</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>사진 붙이는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
+          <t>• 윈도우: Win + Shift + S → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Ctrl + V</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+          <t>• 맥: Cmd + Ctrl + Shift + 4 → 영역 선택 → 엑셀에서 그 줄의 «사진» 칸을 누르고 Cmd + V</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
+          <t>• 사진이 크면 모서리를 끌어 줄이세요. 사진은 그 줄 «사진» 칸 위에 두면 됩니다 — 취합할 때 줄 번호로 찾습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>• 사진은 떠 있는 그대로 두세요(«셀에 배치»로 넣으면 취합할 때 꺼내지 못합니다).</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>누구로 — 계정 바꾸는 법</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• 화면 오른쪽 위 이름을 누르면 사람 목록이 나옵니다. «누구로» 칸의 이름을 누르면 바뀝니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>누구로 — 내 계정 두 개</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>• 계정은 두 개뿐입니다. «누구로» 칸에 계정 이름과 권한이 함께 적혀 있습니다. 비밀번호는 따로 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>이름</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>누구</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>권한</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>볼 수 있는 것</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>주로 하는 것</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>박안전</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과 담당자</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>대부분 이 계정 — 등록·확인·공문</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="5" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>하정수</t>
+          <t>QA박안전5</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소 담당자</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서 일만 한다</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+          <t>재난안전과 담당자</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>모든 부서 · «내 할일»은 전체</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>전 부서 등록·수정 · 확인 · 상신 · 독촉 — 대부분 이 계정</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="51" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>정환경</t>
+          <t>QA하정수5</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>환경과 담당자</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>남의 부서 것을 못 건드리는지 볼 때</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+          <t>담당 공무원 (내 부서: 보건소)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>업무 화면은 전 부서, «내 할일»은 나에게 지정된 것만, 위험성평가 부서별 조치표·교육 이수현황은 내 부서만</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>내 부서 일 · 남의 부서 것을 못 건드리는지 확인</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t>오순환</t>
+          <t>QA시스템관리</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>물순환사업소장</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>자기 부서를 보고 재촉한다</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
+          <t>시스템 관리자 (김유석만)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 메뉴</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>시스템 관리 파일 · 공문 반려(결재 대행)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="5" t="n"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>김중대</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>중대재해팀장</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>공문 결재선(검토)을 볼 때</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>재난안전과장</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다 — 등록 버튼이 없는 게 정상</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>김담양</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>군수</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>보기만 한다</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="5" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>같은 서버를 6명이 함께 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>• 내가 만드는 것(교육 · 근로자 · 문서 · 위원 등)은 이름 앞에 내 이름을 붙입니다 — 예: «김유석_집합교육». 그래야 내 것을 찾기 쉽습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>• 다른 사람이 만든 것은 고치거나 지우지 않습니다. QA박안전5 계정에는 남의 것도 보이는데, 정상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>• 건수·이수율 같은 숫자는 다른 사람이 작업하는 동안 바뀔 수 있습니다. 숫자가 안 맞으면 새로고침해서 한 번 더 보고, 그래도 다르면 «실패».</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>알아 두면 좋은 것 (결함이 아닙니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>• 오늘 날짜가 2026-07-16 으로 고정돼 있습니다. 기한·D-day는 이 날 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>• 입력한 데이터는 그 브라우저 탭에만 남습니다. 새 탭을 열면 처음 상태로 돌아갑니다(새로고침은 괜찮습니다).</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>• 파일 첨부는 파일 이름만 남습니다. 실제 파일을 열거나 받을 수는 없습니다.</t>
+          <t>• 기한·D-day는 서버의 오늘 날짜 기준입니다.</t>
         </is>
       </c>
     </row>
@@ -1392,85 +1358,110 @@
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>• 과장·군수에게 등록·수정 버튼이 없는 것, 결재 승인·반려 버튼이 없는 것(결재는 온나라에서 합니다)은 정상입니다.</t>
+          <t>• «이러면 성공»의 «» 안 문구와 화면 글자가 조금 다르고(띄어쓰기·마침표·어순) 뜻이 같으면 «문의»로 고르고 화면 문구를 메모에 적습니다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>• 2025년 자료는 실제 문서이고, 2026년 자료는 «예시 자료»입니다.</t>
+          <t>• 온나라 연계 전까지 결재는 시스템 안에서 끝납니다 — 상신하면 바로 «결재완료»가 되고 «내부 처리»로 표시됩니다. 결재자가 로그인해 승인할 일은 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>• ---</t>
+          <t>• 로그인은 30분이 지나면 끊깁니다(작업 중이어도). 다시 로그인하고 이어서 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>• 독촉·재촉 알림은 실제 직원에게 가고 되돌릴 수 없습니다. 내 부서 건만 1건씩 누릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>• 과장·팀장이 담당자를 지정하는 흐름과 «내 할일»의 ‹자기 부서 전체› 보기는 과장 계정이 없어 이번 QA 범위 밖입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>• 순서를 놓쳤거나 확인할 자료가 서버에 없으면 «확인 불가»를 고르고 메모에 이유를 적습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
+  <mergeCells count="51">
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="E40:H40"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A52:H52"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"크롬,엣지,웨일,사파리,파이어폭스,기타"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"윈도우 PC,맥,태블릿,휴대폰"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1656,36 +1647,36 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>COUNTA('연계·알림'!$A$4:$A$5)</f>
-        <v>2</v>
+        <f>COUNTA('연계·알림'!$A$4:$A$6)</f>
+        <v>3</v>
       </c>
       <c r="C7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"성공")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"성공")</f>
         <v>0</v>
       </c>
       <c r="D7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"실패")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"실패")</f>
         <v>0</v>
       </c>
       <c r="E7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"오류")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"오류")</f>
         <v>0</v>
       </c>
       <c r="F7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"보류")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"보류")</f>
         <v>0</v>
       </c>
       <c r="G7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"확인 불가")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"확인 불가")</f>
         <v>0</v>
       </c>
       <c r="H7" s="21">
-        <f>COUNTIF('연계·알림'!$G$4:$G$5,"문의")</f>
+        <f>COUNTIF('연계·알림'!$G$4:$G$6,"문의")</f>
         <v>0</v>
       </c>
       <c r="I7" s="21">
-        <f>COUNTBLANK('연계·알림'!$G$4:$G$5)</f>
-        <v>2</v>
+        <f>COUNTBLANK('연계·알림'!$G$4:$G$6)</f>
+        <v>3</v>
       </c>
       <c r="J7" s="22">
         <f>IF(B7=0,0,(B7-I7)/B7)</f>
@@ -1700,7 +1691,7 @@
       </c>
       <c r="B8" s="24">
         <f>SUM(B5:B7)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="24">
         <f>SUM(C5:C7)</f>
@@ -1728,7 +1719,7 @@
       </c>
       <c r="I8" s="24">
         <f>SUM(I5:I7)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="25">
         <f>IF(B8=0,0,(B8-I8)/B8)</f>
@@ -1779,7 +1770,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -1799,7 +1790,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 새 탭에서 시작하세요.</t>
+          <t>🗂 QA시스템관리 계정으로 합니다. 내가 만든 등급 말고는 저장하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1841,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전 → 홍길동</t>
+          <t>QA시스템관리(시스템 관리) → QA하정수5(담당 공무원)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1866,30 +1857,31 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>메뉴 열기</t>
+          <t>누구에게 메뉴가 보이나</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>박안전: 왼쪽 메뉴 8개를 차례로 연다 / 홍길동: 맨 위 메뉴를 본다</t>
+          <t>① QA박안전5 창에서 맨 위 «시스템 관리»를 누르고 왼쪽 메뉴 8개를 차례로 연다
+② QA하정수5 창에서 맨 위 메뉴와 [전체메뉴]를 본다</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8개 화면이 오류 없이 뜬다. 홍길동에게는 «시스템 관리»가 없다</t>
+          <t>QA박안전5 계정: 8개 화면이 오류 없이 뜬다. QA하정수5 계정: «시스템 관리»가 맨 위 메뉴에도 전체메뉴에도 없다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1904,25 +1896,26 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>이름·부서 검색 → 한 사람의 [접근 메뉴]</t>
+          <t>① 사용자 목록 검색창에 내 부서 이름(보건소)을 치고 [검색]
+② 검색을 지우고 내 계정(QA박안전5) 줄의 [접근 메뉴]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>검색대로 걸러지고 그 사람이 쓸 수 있는 메뉴가 보인다</t>
+          <t>검색대로 걸러져 QA하정수5 계정이 나온다. [접근 메뉴] 창에 «접근 가능 …개 / 전체 …개 메뉴»와 메뉴별 보기·수정·근거가 보인다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="96" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1937,25 +1930,28 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>[+ 부서 직접 등록] → 빈 채로 [저장] → 채워서 저장 → [수정] → [사용 중지]</t>
+          <t>① [+ 부서 직접 등록] → 빈 채로 [저장]
+② 부서명 «김유석_QA조직», 유형 «임시조직»으로 [저장]
+③ 그 줄의 [수정] → 부서명을 «김유석_QA조직2»로 [저장]
+④ 그 줄의 [사용 중지]</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>빈 채로는 «부서명을 입력하세요.» 저장·수정이 반영되고 사용 중지 알림이 뜬다</t>
+          <t>빈 채로는 «부서명을 입력하세요.» 저장하면 «조직을 직접 등록했습니다.», 수정하면 «조직 정보를 수정했습니다.»가 뜨고 표에 반영된다. 사용 중지하면 «참조를 보존하고 조직을 사용 중지했습니다.»와 상태 «사용 중지». 출처가 «연계»인 줄에는 «읽기 전용»만 있다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="111" customHeight="1">
       <c r="A7" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1970,25 +1966,28 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>등급을 하나씩 누른다 → [+ 등급 추가]</t>
+          <t>① 왼쪽 등급을 하나씩 눌러 본다(바꾸지 않는다)
+② [+ 등급 추가] → 등급명을 비운 채 [저장]
+③ 등급명 «김유석_QA등급»으로 [저장] (전체 권한·구성원 자동은 체크하지 않고 구성원도 넣지 않는다)
+④ 만든 등급의 [등급 삭제] → 확인</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>등급별 구성원·메뉴 설정이 보이고 시스템 관리자는 «보호»로 표시된다</t>
+          <t>등급마다 구성원·적용 메뉴가 보이고, «시스템 관리자»에는 «보호» 표시가 있고 [등급 삭제]가 없다. 빈 등급명은 «등급명을 입력하세요.» 저장하면 «등급이 추가되었습니다.», 삭제하면 «등급이 삭제되었습니다.»가 뜨고 목록에서 사라진다</t>
         </is>
       </c>
       <c r="G7" s="29" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="96" customHeight="1">
       <c r="A8" s="28" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2003,12 +2002,14 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>메뉴를 누른다 → 권한 설정을 본다 → 메뉴 이름 검색</t>
+          <t>① 왼쪽 메뉴 몇 개를 눌러 오른쪽 접근 권한을 본다
+② 시스템 관리 메뉴 하나를 누른다
+③ 메뉴명 검색창에 «문서» ([저장]·사용 여부 스위치·[다른 메뉴 설정 복사]는 누르지 않는다)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>메뉴가 순서대로 보이고 메뉴에서 뺀 화면에는 «메뉴 제외» 표시가 있다</t>
+          <t>메뉴가 대메뉴 순서대로 보이고 누르면 권한 목록이 나온다. 시스템 관리 메뉴는 시스템 관리자만 접근한다는 안내가 나온다. 메뉴에서 뺀 화면(예: 문서 상세)에는 «메뉴 제외» 표시가 붙어 있다</t>
         </is>
       </c>
       <c r="G8" s="29" t="n"/>
@@ -2067,7 +2068,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2087,7 +2088,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 사업장·양식은 «김유석_…»으로 만든 것만 바꿉니다. 사업장 사용 중지는 정한 시간에 하고 바로 되돌립니다(모두의 화면이 바뀝니다).</t>
         </is>
       </c>
     </row>
@@ -2138,13 +2139,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51" customHeight="1">
+    <row r="4" ht="111" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2154,30 +2155,33 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>등록·편집·사용 중지</t>
+          <t>사업장 등록·편집·사용 중지</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[＋ 사업장 등록] → 빈 채로 [등록] → 채워서 → [편집] → [사용 중지]를 사유 없이 → 사유 넣고</t>
+          <t>① [＋ 사업장 등록] → 사업장명을 비운 채 [등록]
+② 관할 부서는 내 부서(보건소), 사업장명 «김유석_QA사업장»으로 [등록]
+③ 그 줄의 [편집] → 비고를 적고 [저장]
+④ 그 줄의 [사용 중지] → 사유 없이 [사용 중지] → 사유를 적고 [사용 중지]</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>빈 칸이면 «사업장명을 입력하세요.» «사용 중지 사유를 입력하세요.»로 막히고, 채우면 된다</t>
+          <t>빈 칸이면 «사업장명을 입력하세요.» «사용 중지 사유를 입력하세요.»로 막힌다. 등록·저장하면 «사업장이 등록되었습니다.» «사업장이 저장되었습니다.» 사용 중지하면 «사업장이 비활성화되었습니다.»가 뜨고 그 줄에 사유·처리자가 남는다</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>7</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2192,25 +2196,28 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>양식 [편집] → [+ 필드 추가] → [미리보기] → [저장]</t>
+          <t>① 목록의 양식 하나에서 [편집]
+② [+ 새 양식] → 양식명을 «김유석_양식»으로
+③ [+ 필드 추가] → [미리보기] → [닫기]
+④ [저장]</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>편집·미리보기가 된다. 저장은 «…연계 후 제공됩니다»가 뜬다</t>
+          <t>[편집]하면 «…양식을 불러왔습니다»가 뜬다. 미리보기에 추가한 필드가 보인다. [저장]은 «양식 저장은 양식 관리 연계 후 제공됩니다»가 뜨고 목록의 양식은 그대로다</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2225,12 +2232,14 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>자주 찾는 질문 하나 → 검색창에 «교육 시간» → [메뉴 근거 매핑] · [변경 이력] 탭</t>
+          <t>① «자주 찾는 질문» 하나를 누른다
+② 검색창에 «교육 시간»
+③ [메뉴 근거 매핑] 탭 → [변경 이력] 탭 ([매핑 재검토 요청]은 누르지 않는다)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>조문과 «요약 — 원문 아님» 설명이 보이고 검색이 된다. 매핑 탭에는 편집 버튼이 없다</t>
+          <t>조문 원문과 «쉬운 설명 — 요약 — 법적 효력은 원문에 있습니다» 설명이 보이고 검색 결과가 나온다. 매핑 탭에는 편집·저장 버튼이 없다</t>
         </is>
       </c>
       <c r="G6" s="29" t="n"/>
@@ -2285,11 +2294,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -2309,7 +2318,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>🗂 어느 탭에서 해도 됩니다.</t>
+          <t>🗂 바꾼 상태·체크는 같은 줄 안에서 원래대로 돌려 둡니다. 준비 목록 창의 [상태 초기화]는 누르지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -2360,13 +2369,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="111" customHeight="1">
       <c r="A4" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2376,30 +2385,33 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>준비 목록</t>
+          <t>외부 자료 준비 상태</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>[준비 목록 보기] → 한 항목의 상태를 바꾼다 → 닫았다 다시 연다</t>
+          <t>① [준비 목록 보기]
+② 목록 끝쪽에서 «수신 완료»가 아닌 항목 하나를 골라(다른 사람과 겹치지 않게) 지금 상태를 기억하고 «수신 완료»를 누른다
+③ [닫기] → 다시 [준비 목록 보기]
+④ 그 항목을 원래 상태로 되돌린다(아무것도 안 눌려 있었으면 맨 앞 칸)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>고른 상태가 남아 있고 위의 미수신 숫자가 바뀐다</t>
+          <t>누르자마자 그 항목에 «수신 완료» 표시가 붙는다. 다시 열어도 그대로다. ④에서 되돌리면 그 항목이 원래 상태로 돌아간다(위쪽 숫자는 다른 사람 작업으로 달라질 수 있다)</t>
         </is>
       </c>
       <c r="G4" s="29" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>박안전</t>
+          <t>QA시스템관리(시스템 관리)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2409,30 +2421,68 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>알림 규칙</t>
+          <t>알림 규칙 보기</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>규칙 하나를 바꿔 [저장]</t>
+          <t>① 규칙 하나를 열어 채널 칸(화면에 있는 이름 그대로)과 수신자를 본다
+② 바꾸지 않고 닫는다
+③ 아래 발송 이력을 본다</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>«…실제 발송은 외부 채널 연계 후 적용됩니다»가 뜬다. 발송 이력에 «예시 자료» 표시가 있다</t>
+          <t>규칙마다 채널 켜짐·꺼짐과 수신자가 보인다. 켜는 쪽으로는 바꾸지 않는다(실제 직원에게 발송되고 취소되지 않는다)</t>
         </is>
       </c>
       <c r="G5" s="29" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
     </row>
+    <row r="6" ht="81" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>QA시스템관리(시스템 관리)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>관리자 화면 결재 대행</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>공문 반려</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>① 결재 대행 화면에서 교육 파일에서 내가 상신한 «김유석_집합교육» 공문을 찾는다
+② 사유 없이 [반려]
+③ 사유를 넣고 [반려]
+④ QA박안전5 창에서 그 교육을 새로고침한다</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>사유 없이는 막힌다. 반려하면 교육 잠금이 풀리고 [공문 기안]으로 다시 기안할 수 있다</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I5"/>
+  <autoFilter ref="A3:I6"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G5">
+  <conditionalFormatting sqref="G4:G6">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
       <formula>"성공"</formula>
     </cfRule>
@@ -2452,13 +2502,13 @@
       <formula>"문의"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5">
+  <conditionalFormatting sqref="H4:H6">
     <cfRule type="expression" priority="7" dxfId="7">
       <formula>AND(OR($G4="실패",$G4="오류",$G4="문의"),$H4="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G4:G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
+    <dataValidation sqref="G4:G6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르세요" error="결과는 성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중 하나입니다." promptTitle="결과 고르기" prompt="성공 · 실패 · 오류 · 보류 · 확인 불가 · 문의 중에서 고르세요. 실패·오류·문의면 옆 메모에 한 줄." type="list">
       <formula1>"성공,실패,오류,보류,확인 불가,문의"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2544,7 +2594,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
